--- a/artfynd/A 50012-2020 artfynd.xlsx
+++ b/artfynd/A 50012-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123543127</v>
+        <v>123543233</v>
       </c>
       <c r="B2" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661582</v>
+        <v>661545</v>
       </c>
       <c r="R2" t="n">
-        <v>7219162</v>
+        <v>7219178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123543233</v>
+        <v>123543131</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661545</v>
+        <v>661647</v>
       </c>
       <c r="R3" t="n">
-        <v>7219178</v>
+        <v>7219137</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123543051</v>
+        <v>123543237</v>
       </c>
       <c r="B4" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661677</v>
+        <v>661673</v>
       </c>
       <c r="R4" t="n">
-        <v>7219183</v>
+        <v>7219196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123543137</v>
+        <v>123543241</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661413</v>
+        <v>661616</v>
       </c>
       <c r="R5" t="n">
-        <v>7219328</v>
+        <v>7219074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,12 +1081,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1102,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Oskar Wallströmer</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123543234</v>
+        <v>123543240</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661564</v>
+        <v>661616</v>
       </c>
       <c r="R6" t="n">
-        <v>7219175</v>
+        <v>7219080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123543129</v>
+        <v>123543137</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661655</v>
+        <v>661413</v>
       </c>
       <c r="R7" t="n">
-        <v>7219188</v>
+        <v>7219328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,17 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,11 +1321,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123543130</v>
+        <v>123543104</v>
       </c>
       <c r="B8" t="n">
-        <v>79856</v>
+        <v>97350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1349,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661657</v>
+        <v>661624</v>
       </c>
       <c r="R8" t="n">
-        <v>7219159</v>
+        <v>7219058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123543126</v>
+        <v>123543129</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661488</v>
+        <v>661655</v>
       </c>
       <c r="R9" t="n">
-        <v>7219215</v>
+        <v>7219188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På avverkad sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123543235</v>
+        <v>123543051</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1568,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661583</v>
+        <v>661677</v>
       </c>
       <c r="R10" t="n">
-        <v>7219160</v>
+        <v>7219183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123543128</v>
+        <v>123543126</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661686</v>
+        <v>661488</v>
       </c>
       <c r="R11" t="n">
-        <v>7219212</v>
+        <v>7219215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På avverkad sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123543237</v>
+        <v>123543235</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661673</v>
+        <v>661583</v>
       </c>
       <c r="R12" t="n">
-        <v>7219196</v>
+        <v>7219160</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123543240</v>
+        <v>123543130</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661616</v>
+        <v>661657</v>
       </c>
       <c r="R13" t="n">
-        <v>7219080</v>
+        <v>7219159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123543241</v>
+        <v>123543128</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661616</v>
+        <v>661686</v>
       </c>
       <c r="R14" t="n">
-        <v>7219074</v>
+        <v>7219212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2084,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123543238</v>
+        <v>123543278</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>98313</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661629</v>
+        <v>661642</v>
       </c>
       <c r="R15" t="n">
-        <v>7219113</v>
+        <v>7219131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,11 +2192,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran och björk</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123543131</v>
+        <v>123543127</v>
       </c>
       <c r="B16" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661647</v>
+        <v>661582</v>
       </c>
       <c r="R16" t="n">
-        <v>7219137</v>
+        <v>7219162</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123543239</v>
+        <v>123543234</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661628</v>
+        <v>661564</v>
       </c>
       <c r="R17" t="n">
-        <v>7219103</v>
+        <v>7219175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123543104</v>
+        <v>123543238</v>
       </c>
       <c r="B18" t="n">
-        <v>97333</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,25 +2459,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>661624</v>
+        <v>661629</v>
       </c>
       <c r="R18" t="n">
-        <v>7219058</v>
+        <v>7219113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,6 +2523,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran och björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123543278</v>
+        <v>123543239</v>
       </c>
       <c r="B19" t="n">
-        <v>98296</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2571,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>661642</v>
+        <v>661628</v>
       </c>
       <c r="R19" t="n">
-        <v>7219131</v>
+        <v>7219103</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,6 +2635,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 50012-2020 artfynd.xlsx
+++ b/artfynd/A 50012-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123543233</v>
+        <v>123543128</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661545</v>
+        <v>661686</v>
       </c>
       <c r="R2" t="n">
-        <v>7219178</v>
+        <v>7219212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123543131</v>
       </c>
       <c r="B3" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>123543237</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123543241</v>
+        <v>123543051</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661616</v>
+        <v>661677</v>
       </c>
       <c r="R5" t="n">
-        <v>7219074</v>
+        <v>7219183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123543240</v>
+        <v>123543104</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661616</v>
+        <v>661624</v>
       </c>
       <c r="R6" t="n">
-        <v>7219080</v>
+        <v>7219058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,11 +1199,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123543137</v>
+        <v>123543233</v>
       </c>
       <c r="B7" t="n">
-        <v>79898</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661413</v>
+        <v>661545</v>
       </c>
       <c r="R7" t="n">
-        <v>7219328</v>
+        <v>7219178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,12 +1300,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1321,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Oskar Wallströmer</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123543104</v>
+        <v>123543235</v>
       </c>
       <c r="B8" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661624</v>
+        <v>661583</v>
       </c>
       <c r="R8" t="n">
-        <v>7219058</v>
+        <v>7219160</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123543129</v>
+        <v>123543130</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661655</v>
+        <v>661657</v>
       </c>
       <c r="R9" t="n">
-        <v>7219188</v>
+        <v>7219159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123543051</v>
+        <v>123543240</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661677</v>
+        <v>661616</v>
       </c>
       <c r="R10" t="n">
-        <v>7219183</v>
+        <v>7219080</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1681,7 @@
         <v>123543126</v>
       </c>
       <c r="B11" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123543235</v>
+        <v>123543129</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661583</v>
+        <v>661655</v>
       </c>
       <c r="R12" t="n">
-        <v>7219160</v>
+        <v>7219188</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1870,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123543130</v>
+        <v>123543278</v>
       </c>
       <c r="B13" t="n">
-        <v>79862</v>
+        <v>98419</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661657</v>
+        <v>661642</v>
       </c>
       <c r="R13" t="n">
-        <v>7219159</v>
+        <v>7219131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,11 +1978,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123543128</v>
+        <v>123543238</v>
       </c>
       <c r="B14" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661686</v>
+        <v>661629</v>
       </c>
       <c r="R14" t="n">
-        <v>7219212</v>
+        <v>7219113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2089,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran och björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123543278</v>
+        <v>123543241</v>
       </c>
       <c r="B15" t="n">
-        <v>98313</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2133,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661642</v>
+        <v>661616</v>
       </c>
       <c r="R15" t="n">
-        <v>7219131</v>
+        <v>7219074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,6 +2197,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123543127</v>
+        <v>123543137</v>
       </c>
       <c r="B16" t="n">
-        <v>79862</v>
+        <v>79903</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,25 +2245,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2263,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661582</v>
+        <v>661413</v>
       </c>
       <c r="R16" t="n">
-        <v>7219162</v>
+        <v>7219328</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,17 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,11 +2319,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2338,7 +2338,7 @@
         <v>123543234</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123543238</v>
+        <v>123543239</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>661629</v>
+        <v>661628</v>
       </c>
       <c r="R18" t="n">
-        <v>7219113</v>
+        <v>7219103</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran och björk</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123543239</v>
+        <v>123543127</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>661628</v>
+        <v>661582</v>
       </c>
       <c r="R19" t="n">
-        <v>7219103</v>
+        <v>7219162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 50012-2020 artfynd.xlsx
+++ b/artfynd/A 50012-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123543128</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123543131</v>
+        <v>123543278</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661647</v>
+        <v>661642</v>
       </c>
       <c r="R3" t="n">
-        <v>7219137</v>
+        <v>7219131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123543237</v>
+        <v>123543131</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661673</v>
+        <v>661647</v>
       </c>
       <c r="R4" t="n">
-        <v>7219196</v>
+        <v>7219137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123543051</v>
+        <v>123543238</v>
       </c>
       <c r="B5" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661677</v>
+        <v>661629</v>
       </c>
       <c r="R5" t="n">
-        <v>7219183</v>
+        <v>7219113</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran och björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123543104</v>
+        <v>123543126</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1130,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661624</v>
+        <v>661488</v>
       </c>
       <c r="R6" t="n">
-        <v>7219058</v>
+        <v>7219215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På avverkad sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1233,7 @@
         <v>123543233</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123543235</v>
+        <v>123543129</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661583</v>
+        <v>661655</v>
       </c>
       <c r="R8" t="n">
-        <v>7219160</v>
+        <v>7219188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123543130</v>
+        <v>123543127</v>
       </c>
       <c r="B9" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661657</v>
+        <v>661582</v>
       </c>
       <c r="R9" t="n">
-        <v>7219159</v>
+        <v>7219162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123543240</v>
+        <v>123543051</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661616</v>
+        <v>661677</v>
       </c>
       <c r="R10" t="n">
-        <v>7219080</v>
+        <v>7219183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123543126</v>
+        <v>123543237</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661488</v>
+        <v>661673</v>
       </c>
       <c r="R11" t="n">
-        <v>7219215</v>
+        <v>7219196</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På avverkad sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123543129</v>
+        <v>123543104</v>
       </c>
       <c r="B12" t="n">
-        <v>79867</v>
+        <v>97369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661655</v>
+        <v>661624</v>
       </c>
       <c r="R12" t="n">
-        <v>7219188</v>
+        <v>7219058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,11 +1866,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123543278</v>
+        <v>123543137</v>
       </c>
       <c r="B13" t="n">
-        <v>98419</v>
+        <v>79905</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661642</v>
+        <v>661413</v>
       </c>
       <c r="R13" t="n">
-        <v>7219131</v>
+        <v>7219328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,12 +1967,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,11 +1983,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2009,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123543238</v>
+        <v>123543241</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661629</v>
+        <v>661616</v>
       </c>
       <c r="R14" t="n">
-        <v>7219113</v>
+        <v>7219074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2079,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran och björk</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123543241</v>
+        <v>123543235</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661616</v>
+        <v>661583</v>
       </c>
       <c r="R15" t="n">
-        <v>7219074</v>
+        <v>7219160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123543137</v>
+        <v>123543130</v>
       </c>
       <c r="B16" t="n">
-        <v>79903</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,25 +2235,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661413</v>
+        <v>661657</v>
       </c>
       <c r="R16" t="n">
-        <v>7219328</v>
+        <v>7219159</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,12 +2293,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,6 +2314,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Oskar Wallströmer</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2338,7 +2338,7 @@
         <v>123543234</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>123543239</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123543127</v>
+        <v>123543240</v>
       </c>
       <c r="B19" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>661582</v>
+        <v>661616</v>
       </c>
       <c r="R19" t="n">
-        <v>7219162</v>
+        <v>7219080</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 50012-2020 artfynd.xlsx
+++ b/artfynd/A 50012-2020 artfynd.xlsx
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123543127</v>
+        <v>123543051</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>79898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661582</v>
+        <v>661677</v>
       </c>
       <c r="R9" t="n">
-        <v>7219162</v>
+        <v>7219183</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123543051</v>
+        <v>123543237</v>
       </c>
       <c r="B10" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661677</v>
+        <v>661673</v>
       </c>
       <c r="R10" t="n">
-        <v>7219183</v>
+        <v>7219196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123543237</v>
+        <v>123543127</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661673</v>
+        <v>661582</v>
       </c>
       <c r="R11" t="n">
-        <v>7219196</v>
+        <v>7219162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
